--- a/case_studies/base_case_50_5_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2050/technologies.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\base_case_10_dd\2050\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\base_case_50_5_dd\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FDB96DFE316C90107E524FD4235BDA1626C6999C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E884BE-FA78-4BCB-9E52-263751C08958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -685,55 +685,55 @@
         <v>0</v>
       </c>
       <c r="I2" s="3">
-        <v>114.1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>462.87</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
-        <v>99.04</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
-        <v>66.95</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
-        <v>983.99</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>370.48</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
-        <v>416.03</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>36.799999999999997</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
-        <v>22.37</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>181.05</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3">
         <v>0</v>
       </c>
       <c r="V2" s="3">
-        <v>49.16</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3">
-        <v>274.69</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3">
         <v>0</v>
@@ -759,34 +759,34 @@
         <v>32</v>
       </c>
       <c r="B3" s="5">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>45.66</v>
+        <v>0</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="5">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="H3" s="5">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>37.72</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>35.22</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="U3" s="5">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5">
-        <v>48.42</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="5">
         <v>0</v>
@@ -860,73 +860,73 @@
         <v>0</v>
       </c>
       <c r="D4" s="3">
-        <v>39.950000000000003</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3">
-        <v>177.04</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>541.75</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>313.55</v>
+        <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>666.6</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3">
-        <v>666.6</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>1217.3399999999999</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3">
-        <v>1252.6199999999999</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>254.91</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3">
-        <v>43.32</v>
+        <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>490.59</v>
+        <v>0</v>
       </c>
       <c r="U4" s="3">
         <v>0</v>
       </c>
       <c r="V4" s="3">
-        <v>14.73</v>
+        <v>0</v>
       </c>
       <c r="W4" s="3">
-        <v>251.91</v>
+        <v>0</v>
       </c>
       <c r="X4" s="3">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3">
         <v>0</v>
       </c>
       <c r="Z4" s="3">
-        <v>27.91</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
@@ -955,46 +955,46 @@
         <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>216.89</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>38.39</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>109.13</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>425.64</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>161.81</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>166.88</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>745.4</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>745.4</v>
+        <v>0</v>
       </c>
       <c r="O5" s="5">
         <v>0</v>
       </c>
       <c r="P5" s="5">
-        <v>440.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="5">
-        <v>440.9</v>
+        <v>0</v>
       </c>
       <c r="R5" s="5">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5">
-        <v>276.01</v>
+        <v>0</v>
       </c>
       <c r="U5" s="5">
         <v>0</v>
@@ -1012,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="W5" s="5">
-        <v>369.14</v>
+        <v>0</v>
       </c>
       <c r="X5" s="5">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="5">
-        <v>19990</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="5">
-        <v>204.22</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="5">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -1065,40 +1065,40 @@
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>64.790000000000006</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>159.69999999999999</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>166.74</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>187.94</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>187.94</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>526.65</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3">
-        <v>526.65</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3">
-        <v>55.31</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>231.53</v>
+        <v>0</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="3">
-        <v>55.31</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3">
         <v>0</v>
@@ -1160,10 +1160,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>48.52</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -1181,28 +1181,28 @@
         <v>0</v>
       </c>
       <c r="P7" s="5">
-        <v>97.03</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="5">
         <v>0</v>
       </c>
       <c r="R7" s="5">
-        <v>18.48</v>
+        <v>0</v>
       </c>
       <c r="S7" s="5">
-        <v>15.14</v>
+        <v>0</v>
       </c>
       <c r="T7" s="5">
-        <v>48.52</v>
+        <v>0</v>
       </c>
       <c r="U7" s="5">
         <v>0</v>
       </c>
       <c r="V7" s="5">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="W7" s="5">
-        <v>18.38</v>
+        <v>0</v>
       </c>
       <c r="X7" s="5">
         <v>0</v>
@@ -1255,55 +1255,55 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>108.82</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>284.42</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>46.55</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>107.99</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>136.33000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>136.33000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>408.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <v>492.95</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>130.06</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>73.62</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>216.81</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>2.0499999999999998</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
-        <v>311.61</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>19990</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2050/technologies.xlsx
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -712,10 +712,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>230.84</v>
+        <v>230.83</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>274.14</v>
+        <v>274.13</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>37.46</v>
@@ -733,7 +733,7 @@
         <v>46.73</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>235.42</v>
+        <v>235.06</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>6.85</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>448.8</v>
+        <v>222.88</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>897.77</v>
+        <v>745.46</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1369.36</v>
+        <v>1546.46</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1369.36</v>
@@ -906,19 +906,19 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1107.98</v>
+        <v>542.35</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1143.25</v>
+        <v>577.63</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>272.26</v>
+        <v>125.01</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>43.32</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>448.8</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>11.05</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>269.25</v>
+        <v>358.95</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>13.7</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -985,16 +985,16 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>424.14</v>
+        <v>394.11</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>100.9</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>745.4</v>
+        <v>643.22</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>745.4</v>
@@ -1003,34 +1003,34 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>372.73</v>
+        <v>136.9</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>391.69</v>
+        <v>136.9</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>12.77</v>
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>209.33</v>
+        <v>125.97</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>713.5</v>
+        <v>180.98</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>13.7</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>53506.64</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>91.76000000000001</v>
+        <v>59.47</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>347.89</v>
+        <v>37.53</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1079,40 +1079,40 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.88</v>
+        <v>69.53</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>160.23</v>
+        <v>237.55</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>162.15</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>179.06</v>
+        <v>396.62</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>179.06</v>
+        <v>565.33</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>529.65</v>
+        <v>159.51</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>543.11</v>
+        <v>164.81</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>63.82</v>
+        <v>26.47</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9.16</v>
+        <v>9</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>230.03</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>63.82</v>
+        <v>117.06</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>13.7</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>28.97</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.77</v>
+        <v>19.92</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.94</v>
+        <v>16.12</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1218,7 +1218,7 @@
         <v>1.14</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.51</v>
+        <v>19.72</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>136.83</v>
+        <v>136.92</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>288.69</v>
+        <v>288.71</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>81.45999999999999</v>
+        <v>46.32</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>446.76</v>
+        <v>372.28</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>476.68</v>
+        <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>102.09</v>
+        <v>101.99</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>50.33</v>
+        <v>50.26</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>218.29</v>
+        <v>183.24</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,13 +1315,13 @@
         <v>1.54</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>855.89</v>
+        <v>101.58</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>76708.08</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2050/technologies.xlsx
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>115.42</v>
+        <v>114.43</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>453.65</v>
+        <v>458.64</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,16 +712,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>230.83</v>
+        <v>228.86</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>274.13</v>
+        <v>279.52</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>37.46</v>
+        <v>35.44</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>21.27</v>
+        <v>23.37</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>46.73</v>
+        <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>235.06</v>
+        <v>242.02</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>6.85</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
         <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>3.55</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>35.39</v>
@@ -885,19 +885,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>222.88</v>
+        <v>162.78</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>745.46</v>
+        <v>702.62</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0</v>
+        <v>21.35</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1546.46</v>
+        <v>1605.68</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1369.36</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>542.35</v>
+        <v>425.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>577.63</v>
+        <v>467.72</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>125.01</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.32</v>
+        <v>47.61</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>231.42</v>
@@ -924,10 +924,10 @@
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>11.05</v>
+        <v>13.99</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>358.95</v>
+        <v>382.41</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>13.7</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -985,7 +985,7 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>394.11</v>
+        <v>389.77</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>643.22</v>
+        <v>745.4</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>745.4</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>136.9</v>
+        <v>141.05</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>136.9</v>
+        <v>141.05</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>180.98</v>
+        <v>180.32</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>13.7</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>59.47</v>
+        <v>91.61</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37.53</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>69.53</v>
+        <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>237.55</v>
+        <v>242.35</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>396.62</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>565.33</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>159.51</v>
+        <v>134.02</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>164.81</v>
+        <v>139.56</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>26.47</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9</v>
+        <v>9.42</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>117.06</v>
+        <v>121.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>13.7</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>28.97</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.92</v>
+        <v>20.59</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>16.12</v>
+        <v>15.89</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.72</v>
+        <v>19.5</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>-0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>136.92</v>
+        <v>146.63</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>288.71</v>
+        <v>288.62</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46.32</v>
+        <v>-0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,28 +1294,28 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>372.28</v>
+        <v>372.33</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>101.99</v>
+        <v>102.32</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>50.26</v>
+        <v>50.29</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>183.24</v>
+        <v>146.63</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>101.58</v>
+        <v>101.76</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>13.7</v>

--- a/case_studies/base_case_50_5_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2050/technologies.xlsx
@@ -694,13 +694,13 @@
         <v>114.43</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>458.64</v>
+        <v>450.45</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0</v>
+        <v>47.74</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>946.41</v>
@@ -712,10 +712,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>228.86</v>
+        <v>330.31</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>279.52</v>
+        <v>382.68</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>35.44</v>
@@ -724,7 +724,7 @@
         <v>23.37</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>159.94</v>
+        <v>162.17</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>242.02</v>
+        <v>241.7</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>6.85</v>
@@ -885,19 +885,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>162.78</v>
+        <v>56.57</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>702.62</v>
+        <v>546.15</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>21.35</v>
+        <v>221.92</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1605.68</v>
+        <v>1519.72</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1369.36</v>
@@ -906,19 +906,19 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>425.2</v>
+        <v>584.72</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>467.72</v>
+        <v>627.24</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>70.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>47.61</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>231.42</v>
+        <v>278.49</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>13.99</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>382.41</v>
+        <v>357.12</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>13.7</v>
@@ -985,13 +985,13 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>389.77</v>
+        <v>356.02</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>156.59</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>745.4</v>
@@ -1003,34 +1003,34 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>141.05</v>
+        <v>549.62</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>141.05</v>
+        <v>561.59</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>125.97</v>
+        <v>265.02</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>180.32</v>
+        <v>556.0599999999999</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>13.7</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>0</v>
+        <v>41530.27</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1082,46 +1082,46 @@
         <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>242.35</v>
+        <v>174.67</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0</v>
+        <v>165.37</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>197.83</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>565.33</v>
+        <v>197.83</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>134.02</v>
+        <v>487.08</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>139.56</v>
+        <v>508.29</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9.42</v>
+        <v>14.27</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>95.54000000000001</v>
+        <v>233.2</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>121.3</v>
+        <v>75.75</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>13.7</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0</v>
+        <v>35.68</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>20.59</v>
+        <v>19.87</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>15.89</v>
@@ -1218,13 +1218,13 @@
         <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.5</v>
+        <v>48.1</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0</v>
+        <v>2934.72</v>
       </c>
       <c r="Z7" s="5" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>146.63</v>
+        <v>136.69</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>288.62</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>372.33</v>
+        <v>460.93</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>427.03</v>
+        <v>490.77</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>102.32</v>
@@ -1306,7 +1306,7 @@
         <v>50.29</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>146.63</v>
+        <v>217.01</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,13 +1315,13 @@
         <v>2.05</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>101.76</v>
+        <v>692.63</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>61254.54</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2050/technologies.xlsx
@@ -691,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>114.43</v>
+        <v>115.26</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>450.45</v>
+        <v>458.64</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>47.74</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>946.41</v>
@@ -712,10 +712,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>330.31</v>
+        <v>230.52</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>382.68</v>
+        <v>279.52</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>35.44</v>
@@ -724,7 +724,7 @@
         <v>23.37</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>162.17</v>
+        <v>159.94</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>241.7</v>
+        <v>242.02</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>6.85</v>
@@ -873,7 +873,7 @@
         <v>39.95</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -885,19 +885,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>56.57</v>
+        <v>185.68</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>546.15</v>
+        <v>734.3099999999999</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>221.92</v>
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1519.72</v>
+        <v>1614.83</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1369.36</v>
@@ -906,19 +906,19 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>584.72</v>
+        <v>408.22</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>627.24</v>
+        <v>450.75</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0</v>
+        <v>47.72</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>47.61</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>278.49</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>13.99</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>357.12</v>
+        <v>385.11</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>13.7</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -985,13 +985,13 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>356.02</v>
+        <v>394.41</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>156.59</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>745.4</v>
@@ -1003,34 +1003,34 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>549.62</v>
+        <v>136.61</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>561.59</v>
+        <v>136.61</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>265.02</v>
+        <v>125.97</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>556.0599999999999</v>
+        <v>181.02</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>13.7</v>
+        <v>0.47</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>41530.27</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.81</v>
+        <v>-0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1082,46 +1082,46 @@
         <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>174.67</v>
+        <v>240.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>165.37</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>197.83</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>197.83</v>
+        <v>565.33</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>487.08</v>
+        <v>134.02</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>508.29</v>
+        <v>139.56</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>14.27</v>
+        <v>9.42</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>233.2</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>75.75</v>
+        <v>121.27</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>13.7</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>35.68</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.87</v>
+        <v>20.59</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>15.89</v>
@@ -1218,13 +1218,13 @@
         <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>48.1</v>
+        <v>19.5</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>2934.72</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="5" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>80.31999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>460.93</v>
+        <v>372.33</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>490.77</v>
+        <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>102.32</v>
+        <v>128.06</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>50.29</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>217.01</v>
+        <v>136.69</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,13 +1315,13 @@
         <v>2.05</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>692.63</v>
+        <v>101.76</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>61254.54</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2050/technologies.xlsx
@@ -736,7 +736,7 @@
         <v>242.02</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>185.68</v>
+        <v>183.49</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>734.3099999999999</v>
+        <v>726.39</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1614.83</v>
+        <v>1601.88</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1369.36</v>
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>408.22</v>
+        <v>432.25</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>450.75</v>
+        <v>474.77</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>47.72</v>
+        <v>84.47</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>47.61</v>
@@ -927,7 +927,7 @@
         <v>13.99</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>385.11</v>
+        <v>381.3</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>13.7</v>
@@ -985,7 +985,7 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>394.41</v>
+        <v>416.99</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>181.02</v>
+        <v>184.44</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>0.47</v>
+        <v>13.7</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>20.59</v>
+        <v>20.6</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>15.89</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>128.06</v>
+        <v>128.05</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>50.29</v>
@@ -1318,7 +1318,7 @@
         <v>101.76</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>13.7</v>
+        <v>6.7</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
